--- a/pensum/ok06/LOM_Ovingsark_Okonomistyring_kap06_Kapitalbehov_NY.xlsx
+++ b/pensum/ok06/LOM_Ovingsark_Okonomistyring_kap06_Kapitalbehov_NY.xlsx
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="B46" s="10" t="n">
-        <v>11650000</v>
+        <v>8390000</v>
       </c>
     </row>
     <row r="47">

--- a/pensum/ok06/LOM_Ovingsark_Okonomistyring_kap06_Kapitalbehov_NY.xlsx
+++ b/pensum/ok06/LOM_Ovingsark_Okonomistyring_kap06_Kapitalbehov_NY.xlsx
@@ -337,7 +337,7 @@
     <t xml:space="preserve">Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Bok 1.</t>
+    <t xml:space="preserve">Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Økonomistyring for LØM-emnet.</t>
   </si>
   <si>
     <t xml:space="preserve">Hvor mye penger må du ha før du åpner?</t>
@@ -496,7 +496,7 @@
     <t xml:space="preserve">Prøv dette: sett kredittiden i B23 til 40 dager og se hva som skjer med B31. Det er oppgave A1 i øvingsheftet.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 6.1 med underavsnitt. Tallene er oppstarten av Nordlys Elektro AS i 2019.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 6.1 med underavsnitt. Tallene er oppstarten av Nordlys Elektro AS i 2019.</t>
   </si>
   <si>
     <t xml:space="preserve">Hva kredittiden gjør med kapitalbehovet</t>
@@ -577,7 +577,7 @@
     <t xml:space="preserve">Binder null dagers kredittid null kroner?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 6.1.3 om kundefordringer. Tallene er Nordlys Elektro AS' egne.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 6.1.3 om kundefordringer. Tallene er Nordlys Elektro AS' egne.</t>
   </si>
   <si>
     <t xml:space="preserve">Hvem skal skaffe pengene?</t>
@@ -718,7 +718,7 @@
     <t xml:space="preserve">Prøv dette: sett egenkapitalen i B20 og se på B21 og B24. Det er oppgave A2.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 6.2 om finansieringsplanen og 6.3 om åpningsbalansen.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 6.2 om finansieringsplanen og 6.3 om åpningsbalansen.</t>
   </si>
   <si>
     <t xml:space="preserve">Tre scenarioer</t>
@@ -931,7 +931,7 @@
     <t xml:space="preserve">Her SKAL det stå AVVIK med tallene som ligger inne. Det er hele saken: pengene finnes, men de står hos kundene og på lageret.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 6.1.3 om kundefordringer og 6.5 om kassekreditt. Tallene for 2026 er Nordlys Elektro AS' eget regnskap, det samme du leser i kapittel 3 og budsjetterer videre på i kapittel 9. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 6.1.3 om kundefordringer og 6.5 om kassekreditt. Tallene for 2026 er Nordlys Elektro AS' eget regnskap, det samme du leser i kapittel 3 og budsjetterer videre på i kapittel 9. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
   </si>
   <si>
     <t xml:space="preserve">Din egen bedrift</t>
